--- a/12600512.xlsx
+++ b/12600512.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\vaults\my vault\01-academics\01-semester\02-cap776-python\04-assignments\daily-activity-tracker\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72DEC278-6671-4D9C-9A78-F69240517425}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{032597EF-127E-4D1A-9F31-764A40F0DF86}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="12" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="63">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -1356,42 +1356,62 @@
       <c r="C14" s="9">
         <v>0</v>
       </c>
-      <c r="D14" s="9"/>
-      <c r="E14" s="9"/>
-      <c r="F14" s="9"/>
-      <c r="G14" s="9"/>
-      <c r="H14" s="9"/>
+      <c r="D14" s="9">
+        <v>120</v>
+      </c>
+      <c r="E14" s="9">
+        <v>0</v>
+      </c>
+      <c r="F14" s="9">
+        <v>350</v>
+      </c>
+      <c r="G14" s="9">
+        <v>7</v>
+      </c>
+      <c r="H14" s="9">
+        <v>0</v>
+      </c>
       <c r="I14" s="10">
         <f t="shared" si="0"/>
-        <v>480</v>
+        <v>950</v>
       </c>
       <c r="J14" s="10">
         <f t="shared" si="1"/>
-        <v>960</v>
-      </c>
-      <c r="K14" s="11"/>
-      <c r="L14" s="11"/>
-      <c r="M14" s="11"/>
+        <v>490</v>
+      </c>
+      <c r="K14" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="L14" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="M14" s="11" t="s">
+        <v>51</v>
+      </c>
       <c r="N14" s="12"/>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A15" s="8">
         <v>46260</v>
       </c>
-      <c r="B15" s="9"/>
-      <c r="C15" s="9"/>
+      <c r="B15" s="9">
+        <v>420</v>
+      </c>
+      <c r="C15" s="9">
+        <v>0</v>
+      </c>
       <c r="D15" s="9"/>
       <c r="E15" s="9"/>
       <c r="F15" s="9"/>
       <c r="G15" s="9"/>
       <c r="H15" s="9"/>
-      <c r="I15" s="10" t="str">
+      <c r="I15" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J15" s="10" t="str">
+        <v>420</v>
+      </c>
+      <c r="J15" s="10">
         <f t="shared" si="1"/>
-        <v/>
+        <v>1020</v>
       </c>
       <c r="K15" s="11"/>
       <c r="L15" s="11"/>

--- a/12600512.xlsx
+++ b/12600512.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\vaults\my vault\01-academics\01-semester\02-cap776-python\04-assignments\daily-activity-tracker\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{032597EF-127E-4D1A-9F31-764A40F0DF86}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55E95A68-3B43-4260-AC01-DB7628BB784C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="12" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="63">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -1400,46 +1400,82 @@
       <c r="C15" s="9">
         <v>0</v>
       </c>
-      <c r="D15" s="9"/>
-      <c r="E15" s="9"/>
-      <c r="F15" s="9"/>
-      <c r="G15" s="9"/>
-      <c r="H15" s="9"/>
+      <c r="D15" s="9">
+        <v>120</v>
+      </c>
+      <c r="E15" s="9">
+        <v>60</v>
+      </c>
+      <c r="F15" s="9">
+        <v>350</v>
+      </c>
+      <c r="G15" s="9">
+        <v>7</v>
+      </c>
+      <c r="H15" s="9">
+        <v>0</v>
+      </c>
       <c r="I15" s="10">
         <f t="shared" si="0"/>
-        <v>420</v>
+        <v>950</v>
       </c>
       <c r="J15" s="10">
         <f t="shared" si="1"/>
-        <v>1020</v>
-      </c>
-      <c r="K15" s="11"/>
-      <c r="L15" s="11"/>
-      <c r="M15" s="11"/>
+        <v>490</v>
+      </c>
+      <c r="K15" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="L15" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="M15" s="11" t="s">
+        <v>51</v>
+      </c>
       <c r="N15" s="12"/>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A16" s="8">
         <v>46261</v>
       </c>
-      <c r="B16" s="9"/>
-      <c r="C16" s="9"/>
-      <c r="D16" s="9"/>
-      <c r="E16" s="9"/>
-      <c r="F16" s="9"/>
-      <c r="G16" s="9"/>
-      <c r="H16" s="9"/>
-      <c r="I16" s="10" t="str">
+      <c r="B16" s="9">
+        <v>480</v>
+      </c>
+      <c r="C16" s="9">
+        <v>0</v>
+      </c>
+      <c r="D16" s="9">
+        <v>120</v>
+      </c>
+      <c r="E16" s="9">
+        <v>120</v>
+      </c>
+      <c r="F16" s="9">
+        <v>200</v>
+      </c>
+      <c r="G16" s="9">
+        <v>4</v>
+      </c>
+      <c r="H16" s="9">
+        <v>0</v>
+      </c>
+      <c r="I16" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J16" s="10" t="str">
+        <v>920</v>
+      </c>
+      <c r="J16" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K16" s="11"/>
-      <c r="L16" s="11"/>
-      <c r="M16" s="11"/>
+        <v>520</v>
+      </c>
+      <c r="K16" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="L16" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="M16" s="11" t="s">
+        <v>51</v>
+      </c>
       <c r="N16" s="12"/>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.3">

--- a/12600512.xlsx
+++ b/12600512.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\vaults\my vault\01-academics\01-semester\02-cap776-python\04-assignments\daily-activity-tracker\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55E95A68-3B43-4260-AC01-DB7628BB784C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08C27D8B-9708-473B-90B4-DCEEB9A962F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="65">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -224,6 +224,12 @@
   </si>
   <si>
     <t>Feeling lazy</t>
+  </si>
+  <si>
+    <t>Today I started going to the library.</t>
+  </si>
+  <si>
+    <t>Second day of library.</t>
   </si>
 </sst>
 </file>
@@ -1482,73 +1488,137 @@
       <c r="A17" s="8">
         <v>46262</v>
       </c>
-      <c r="B17" s="9"/>
-      <c r="C17" s="9"/>
-      <c r="D17" s="9"/>
-      <c r="E17" s="9"/>
-      <c r="F17" s="9"/>
-      <c r="G17" s="9"/>
-      <c r="H17" s="9"/>
-      <c r="I17" s="10" t="str">
+      <c r="B17" s="9">
+        <v>360</v>
+      </c>
+      <c r="C17" s="9">
+        <v>0</v>
+      </c>
+      <c r="D17" s="9">
+        <v>120</v>
+      </c>
+      <c r="E17" s="9">
+        <v>60</v>
+      </c>
+      <c r="F17" s="9">
+        <v>150</v>
+      </c>
+      <c r="G17" s="9">
+        <v>3</v>
+      </c>
+      <c r="H17" s="9">
+        <v>0</v>
+      </c>
+      <c r="I17" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J17" s="10" t="str">
+        <v>690</v>
+      </c>
+      <c r="J17" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K17" s="11"/>
-      <c r="L17" s="11"/>
-      <c r="M17" s="11"/>
+        <v>750</v>
+      </c>
+      <c r="K17" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="L17" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="M17" s="11" t="s">
+        <v>51</v>
+      </c>
       <c r="N17" s="12"/>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A18" s="8">
         <v>46263</v>
       </c>
-      <c r="B18" s="9"/>
-      <c r="C18" s="9"/>
-      <c r="D18" s="9"/>
-      <c r="E18" s="9"/>
-      <c r="F18" s="9"/>
-      <c r="G18" s="9"/>
-      <c r="H18" s="9"/>
-      <c r="I18" s="10" t="str">
+      <c r="B18" s="9">
+        <v>420</v>
+      </c>
+      <c r="C18" s="9">
+        <v>0</v>
+      </c>
+      <c r="D18" s="9">
+        <v>400</v>
+      </c>
+      <c r="E18" s="9">
+        <v>120</v>
+      </c>
+      <c r="F18" s="9">
+        <v>0</v>
+      </c>
+      <c r="G18" s="9">
+        <v>0</v>
+      </c>
+      <c r="H18" s="9">
+        <v>0</v>
+      </c>
+      <c r="I18" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J18" s="10" t="str">
+        <v>940</v>
+      </c>
+      <c r="J18" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K18" s="11"/>
-      <c r="L18" s="11"/>
-      <c r="M18" s="11"/>
-      <c r="N18" s="12"/>
+        <v>500</v>
+      </c>
+      <c r="K18" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="L18" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="M18" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="N18" s="12" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A19" s="8">
         <v>46264</v>
       </c>
-      <c r="B19" s="9"/>
-      <c r="C19" s="9"/>
-      <c r="D19" s="9"/>
-      <c r="E19" s="9"/>
-      <c r="F19" s="9"/>
-      <c r="G19" s="9"/>
-      <c r="H19" s="9"/>
-      <c r="I19" s="10" t="str">
+      <c r="B19" s="9">
+        <v>480</v>
+      </c>
+      <c r="C19" s="9">
+        <v>0</v>
+      </c>
+      <c r="D19" s="9">
+        <v>240</v>
+      </c>
+      <c r="E19" s="9">
+        <v>120</v>
+      </c>
+      <c r="F19" s="9">
+        <v>0</v>
+      </c>
+      <c r="G19" s="9">
+        <v>0</v>
+      </c>
+      <c r="H19" s="9">
+        <v>0</v>
+      </c>
+      <c r="I19" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J19" s="10" t="str">
+        <v>840</v>
+      </c>
+      <c r="J19" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K19" s="11"/>
-      <c r="L19" s="11"/>
-      <c r="M19" s="11"/>
-      <c r="N19" s="12"/>
+        <v>600</v>
+      </c>
+      <c r="K19" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="L19" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="M19" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="N19" s="12" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A20" s="8">

--- a/12600512.xlsx
+++ b/12600512.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\vaults\my vault\01-academics\01-semester\02-cap776-python\04-assignments\daily-activity-tracker\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08C27D8B-9708-473B-90B4-DCEEB9A962F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0F38389-EFA7-4773-9D39-8C26DD93EB3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="68">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -230,6 +230,15 @@
   </si>
   <si>
     <t>Second day of library.</t>
+  </si>
+  <si>
+    <t>Unsatisfied</t>
+  </si>
+  <si>
+    <t>Today I got our 4th HOS interaction</t>
+  </si>
+  <si>
+    <t>I start solving problems in codewars</t>
   </si>
 </sst>
 </file>
@@ -1624,113 +1633,225 @@
       <c r="A20" s="8">
         <v>46265</v>
       </c>
-      <c r="B20" s="9"/>
-      <c r="C20" s="9"/>
-      <c r="D20" s="9"/>
-      <c r="E20" s="9"/>
-      <c r="F20" s="9"/>
-      <c r="G20" s="9"/>
-      <c r="H20" s="9"/>
-      <c r="I20" s="10" t="str">
+      <c r="B20" s="9">
+        <v>420</v>
+      </c>
+      <c r="C20" s="9">
+        <v>0</v>
+      </c>
+      <c r="D20" s="9">
+        <v>300</v>
+      </c>
+      <c r="E20" s="9">
+        <v>120</v>
+      </c>
+      <c r="F20" s="9">
+        <v>200</v>
+      </c>
+      <c r="G20" s="9">
+        <v>4</v>
+      </c>
+      <c r="H20" s="9">
+        <v>0</v>
+      </c>
+      <c r="I20" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J20" s="10" t="str">
+        <v>1040</v>
+      </c>
+      <c r="J20" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K20" s="11"/>
-      <c r="L20" s="11"/>
-      <c r="M20" s="11"/>
+        <v>400</v>
+      </c>
+      <c r="K20" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="L20" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="M20" s="11" t="s">
+        <v>51</v>
+      </c>
       <c r="N20" s="12"/>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A21" s="8"/>
-      <c r="B21" s="9"/>
-      <c r="C21" s="9"/>
-      <c r="D21" s="9"/>
-      <c r="E21" s="9"/>
-      <c r="F21" s="9"/>
-      <c r="G21" s="9"/>
-      <c r="H21" s="9"/>
-      <c r="I21" s="10" t="str">
+      <c r="A21" s="8">
+        <v>46266</v>
+      </c>
+      <c r="B21" s="9">
+        <v>400</v>
+      </c>
+      <c r="C21" s="9">
+        <v>0</v>
+      </c>
+      <c r="D21" s="9">
+        <v>120</v>
+      </c>
+      <c r="E21" s="9">
+        <v>80</v>
+      </c>
+      <c r="F21" s="9">
+        <v>350</v>
+      </c>
+      <c r="G21" s="9">
+        <v>7</v>
+      </c>
+      <c r="H21" s="9">
+        <v>0</v>
+      </c>
+      <c r="I21" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J21" s="10" t="str">
+        <v>950</v>
+      </c>
+      <c r="J21" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K21" s="11"/>
-      <c r="L21" s="11"/>
-      <c r="M21" s="11"/>
+        <v>490</v>
+      </c>
+      <c r="K21" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="L21" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="M21" s="11" t="s">
+        <v>51</v>
+      </c>
       <c r="N21" s="12"/>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A22" s="8"/>
-      <c r="B22" s="9"/>
-      <c r="C22" s="9"/>
-      <c r="D22" s="9"/>
-      <c r="E22" s="9"/>
-      <c r="F22" s="9"/>
-      <c r="G22" s="9"/>
-      <c r="H22" s="9"/>
-      <c r="I22" s="10" t="str">
+      <c r="A22" s="8">
+        <v>46267</v>
+      </c>
+      <c r="B22" s="9">
+        <v>460</v>
+      </c>
+      <c r="C22" s="9">
+        <v>0</v>
+      </c>
+      <c r="D22" s="9">
+        <v>200</v>
+      </c>
+      <c r="E22" s="9">
+        <v>60</v>
+      </c>
+      <c r="F22" s="9">
+        <v>350</v>
+      </c>
+      <c r="G22" s="9">
+        <v>7</v>
+      </c>
+      <c r="H22" s="9">
+        <v>0</v>
+      </c>
+      <c r="I22" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J22" s="10" t="str">
+        <v>1070</v>
+      </c>
+      <c r="J22" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K22" s="11"/>
-      <c r="L22" s="11"/>
-      <c r="M22" s="11"/>
+        <v>370</v>
+      </c>
+      <c r="K22" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="L22" s="11" t="s">
+        <v>65</v>
+      </c>
+      <c r="M22" s="11" t="s">
+        <v>51</v>
+      </c>
       <c r="N22" s="12"/>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A23" s="8"/>
-      <c r="B23" s="9"/>
-      <c r="C23" s="9"/>
-      <c r="D23" s="9"/>
-      <c r="E23" s="9"/>
-      <c r="F23" s="9"/>
-      <c r="G23" s="9"/>
-      <c r="H23" s="9"/>
-      <c r="I23" s="10" t="str">
+      <c r="A23" s="8">
+        <v>46268</v>
+      </c>
+      <c r="B23" s="9">
+        <v>420</v>
+      </c>
+      <c r="C23" s="9">
+        <v>0</v>
+      </c>
+      <c r="D23" s="9">
+        <v>300</v>
+      </c>
+      <c r="E23" s="9">
+        <v>180</v>
+      </c>
+      <c r="F23" s="9">
+        <v>200</v>
+      </c>
+      <c r="G23" s="9">
+        <v>4</v>
+      </c>
+      <c r="H23" s="9">
+        <v>0</v>
+      </c>
+      <c r="I23" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J23" s="10" t="str">
+        <v>1100</v>
+      </c>
+      <c r="J23" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K23" s="11"/>
-      <c r="L23" s="11"/>
-      <c r="M23" s="11"/>
-      <c r="N23" s="12"/>
+        <v>340</v>
+      </c>
+      <c r="K23" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="L23" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="M23" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="N23" s="12" t="s">
+        <v>67</v>
+      </c>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A24" s="8"/>
-      <c r="B24" s="9"/>
-      <c r="C24" s="9"/>
-      <c r="D24" s="9"/>
-      <c r="E24" s="9"/>
-      <c r="F24" s="9"/>
-      <c r="G24" s="9"/>
-      <c r="H24" s="9"/>
-      <c r="I24" s="10" t="str">
+      <c r="A24" s="8">
+        <v>46269</v>
+      </c>
+      <c r="B24" s="9">
+        <v>300</v>
+      </c>
+      <c r="C24" s="9">
+        <v>0</v>
+      </c>
+      <c r="D24" s="9">
+        <v>240</v>
+      </c>
+      <c r="E24" s="9">
+        <v>120</v>
+      </c>
+      <c r="F24" s="9">
+        <v>250</v>
+      </c>
+      <c r="G24" s="9">
+        <v>5</v>
+      </c>
+      <c r="H24" s="9">
+        <v>0</v>
+      </c>
+      <c r="I24" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J24" s="10" t="str">
+        <v>910</v>
+      </c>
+      <c r="J24" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K24" s="11"/>
-      <c r="L24" s="11"/>
-      <c r="M24" s="11"/>
-      <c r="N24" s="12"/>
+        <v>530</v>
+      </c>
+      <c r="K24" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="L24" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="M24" s="11" t="s">
+        <v>61</v>
+      </c>
+      <c r="N24" s="12" t="s">
+        <v>66</v>
+      </c>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A25" s="8"/>
